--- a/downloads/excel/Ключевые_обязанности_субъектов_по_ЗСГО.xlsx
+++ b/downloads/excel/Ключевые_обязанности_субъектов_по_ЗСГО.xlsx
@@ -480,7 +480,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -554,6 +553,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>